--- a/coils_model/data/N2.xlsx
+++ b/coils_model/data/N2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\coils_model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F4E0EB-EB49-4C90-8B88-A78EA49BA019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AEF1BE-DEAB-439D-819B-09F0664FF921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23FBE2E8-3412-4CB8-A195-BDEE40B55461}"/>
+    <workbookView xWindow="12450" yWindow="915" windowWidth="14850" windowHeight="12270" xr2:uid="{23FBE2E8-3412-4CB8-A195-BDEE40B55461}"/>
   </bookViews>
   <sheets>
     <sheet name="N2" sheetId="1" r:id="rId1"/>
@@ -242,7 +242,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -420,6 +420,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -667,8 +673,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -716,7 +725,7 @@
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -728,13 +737,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5592,48 +5594,48 @@
         <v>74.893385660000007</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A102">
-        <v>2</v>
-      </c>
-      <c r="B102">
+    <row r="102" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>2</v>
+      </c>
+      <c r="B102" s="1">
         <v>30</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>0.8</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="1">
         <v>69.900000000000006</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="1">
         <v>0.8</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="1">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="G102">
+      <c r="G102" s="1">
         <f t="shared" si="5"/>
         <v>26.8</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
         <f t="shared" si="6"/>
         <v>0.28959954257812492</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="1">
         <f t="shared" si="7"/>
         <v>3.4079999999999999E-2</v>
       </c>
-      <c r="J102">
-        <v>6.78</v>
-      </c>
-      <c r="K102">
+      <c r="J102" s="1">
+        <v>6.78</v>
+      </c>
+      <c r="K102" s="1">
         <v>1.8447351000000001E-2</v>
       </c>
-      <c r="L102">
+      <c r="L102" s="1">
         <v>0.14243311</v>
       </c>
-      <c r="M102">
+      <c r="M102" s="1">
         <v>5.5173764810000003</v>
       </c>
     </row>
@@ -46185,11 +46187,11 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="I3">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$H2*1.05&lt;$K2</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I2*0.9&gt;$L2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$H2*1.05&lt;$K2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
